--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -63,22 +63,34 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
+    <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDISSA ABASTAS AMANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brgy 4, City Of Koronadal (Capital), South Cotabato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-X-06965</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1403-812</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cashier edge</x:t>
+  </x:si>
+  <x:si>
     <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
-    <x:t>EDISSA ABASTAS AMANTE</x:t>
-  </x:si>
-  <x:si>
     <x:t>REN</x:t>
   </x:si>
   <x:si>
-    <x:t>Brgy 4, City Of Koronadal (Capital), South Cotabato</x:t>
-  </x:si>
-  <x:si>
     <x:t>61-3-2026-1402-290</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cashier edge</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -411,7 +423,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -437,13 +449,10 @@
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -526,12 +535,12 @@
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -943,94 +952,128 @@
       <x:c r="E6" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="n">
-        <x:v>123456789</x:v>
+      <x:c r="F6" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46091.059537037</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46050</x:v>
+        <x:v>46091.1148611111</x:v>
+      </x:c>
+      <x:c r="I6" s="12">
+        <x:v>46091.143125</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>165163</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>300</x:v>
+        <x:v>125646</x:v>
+      </x:c>
+      <x:c r="K6" s="13" t="n">
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46091.0629861111</x:v>
+        <x:v>46091.1453125</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="N6" s="7" t="s"/>
       <x:c r="O6" s="9" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
+      <x:c r="B7" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="n">
+        <x:v>123456789</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H7" s="12">
+        <x:v>46091.059537037</x:v>
+      </x:c>
+      <x:c r="I7" s="14">
+        <x:v>46050</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="n">
+        <x:v>165163</x:v>
+      </x:c>
+      <x:c r="K7" s="13" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L7" s="12">
+        <x:v>46091.0629861111</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="s"/>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="17" t="s"/>
-      <x:c r="F9" s="17" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="s"/>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="17" t="s"/>
+      <x:c r="F10" s="17" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="18" t="s">
+    <x:row r="11" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B11" s="18" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="20" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B12" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="21" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C10" s="19" t="s"/>
-      <x:c r="D10" s="19" t="s"/>
-      <x:c r="E10" s="19" t="s"/>
-      <x:c r="F10" s="20" t="s">
-        <x:v>21</x:v>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="23" t="n">
-        <x:v>1</x:v>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2011,13 +2054,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="7">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
+    <x:mergeCell ref="B10:F10"/>
     <x:mergeCell ref="B11:E11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -9,58 +9,22 @@
     <x:sheet name="March 2026" sheetId="7" r:id="rId7"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -139,12 +103,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -155,16 +113,30 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -180,13 +152,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -217,12 +182,12 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -234,14 +199,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -423,7 +388,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -434,160 +399,186 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -851,226 +842,228 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46091.1148611111</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46091.143125</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>125646</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46091.1453125</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="n">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="n">
         <x:v>123456789</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="G7" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
         <x:v>46091.059537037</x:v>
       </x:c>
-      <x:c r="I7" s="14">
+      <x:c r="I7" s="18">
         <x:v>46050</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="16" t="n">
         <x:v>165163</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="K7" s="19" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="17">
         <x:v>46091.0629861111</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s"/>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="17" t="s"/>
-      <x:c r="F10" s="17" t="s"/>
+      <x:c r="B10" s="20" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="22" t="s"/>
+      <x:c r="F10" s="22" t="s"/>
     </x:row>
     <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="20" t="s">
-        <x:v>25</x:v>
+      <x:c r="B11" s="23" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="26" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>CERTIFICATE SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -1014,61 +1014,61 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="22" t="s"/>
-      <x:c r="F10" s="22" t="s"/>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
     </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="s">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2047,14 +2047,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B10:F10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -463,7 +463,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -499,39 +499,43 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -905,7 +909,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -945,7 +949,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>8</x:v>
@@ -985,87 +989,87 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="20" t="s"/>
+      <x:c r="C8" s="20" t="s"/>
+      <x:c r="D8" s="20" t="s"/>
+      <x:c r="E8" s="20" t="s"/>
+      <x:c r="F8" s="20" t="s"/>
+      <x:c r="G8" s="20" t="s"/>
+      <x:c r="H8" s="20" t="s"/>
+      <x:c r="I8" s="20" t="s"/>
+      <x:c r="J8" s="20" t="s"/>
+      <x:c r="K8" s="20" t="s"/>
+      <x:c r="L8" s="20" t="s"/>
+      <x:c r="M8" s="20" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="20" t="s"/>
+      <x:c r="C9" s="20" t="s"/>
+      <x:c r="D9" s="20" t="s"/>
+      <x:c r="E9" s="20" t="s"/>
+      <x:c r="F9" s="20" t="s"/>
+      <x:c r="G9" s="20" t="s"/>
+      <x:c r="H9" s="20" t="s"/>
+      <x:c r="I9" s="20" t="s"/>
+      <x:c r="J9" s="20" t="s"/>
+      <x:c r="K9" s="20" t="s"/>
+      <x:c r="L9" s="20" t="s"/>
+      <x:c r="M9" s="20" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="23" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="24" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="27" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="27" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
+      <x:c r="B16" s="30" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -879,7 +879,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -949,7 +949,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>8</x:v>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,9 +22,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <x:si>
     <x:t>CERTIFICATE SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -121,22 +157,14 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -152,6 +180,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -388,7 +423,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -399,71 +434,65 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -494,95 +523,71 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -881,18 +886,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -910,166 +903,178 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46091.1148611111</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46091.143125</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>125646</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46091.1453125</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="n">
-        <x:v>123456789</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46091.059537037</x:v>
-      </x:c>
-      <x:c r="I7" s="18">
-        <x:v>46050</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>165163</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46091.0629861111</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>7</x:v>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="20" t="s"/>
-      <x:c r="C8" s="20" t="s"/>
-      <x:c r="D8" s="20" t="s"/>
-      <x:c r="E8" s="20" t="s"/>
-      <x:c r="F8" s="20" t="s"/>
-      <x:c r="G8" s="20" t="s"/>
-      <x:c r="H8" s="20" t="s"/>
-      <x:c r="I8" s="20" t="s"/>
-      <x:c r="J8" s="20" t="s"/>
-      <x:c r="K8" s="20" t="s"/>
-      <x:c r="L8" s="20" t="s"/>
-      <x:c r="M8" s="20" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46091.1148611111</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46091.143125</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>125646</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46091.1453125</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="20" t="s"/>
-      <x:c r="C9" s="20" t="s"/>
-      <x:c r="D9" s="20" t="s"/>
-      <x:c r="E9" s="20" t="s"/>
-      <x:c r="F9" s="20" t="s"/>
-      <x:c r="G9" s="20" t="s"/>
-      <x:c r="H9" s="20" t="s"/>
-      <x:c r="I9" s="20" t="s"/>
-      <x:c r="J9" s="20" t="s"/>
-      <x:c r="K9" s="20" t="s"/>
-      <x:c r="L9" s="20" t="s"/>
-      <x:c r="M9" s="20" t="s"/>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="n">
+        <x:v>123456789</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46091.059537037</x:v>
+      </x:c>
+      <x:c r="I9" s="14">
+        <x:v>46050</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>165163</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46091.0629861111</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
+      <x:c r="B12" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s"/>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="17" t="s"/>
+      <x:c r="F12" s="17" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
-        <x:v>13</x:v>
+      <x:c r="B13" s="18" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="20" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -423,11 +423,14 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -492,7 +495,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -522,6 +525,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -836,7 +843,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46082</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -908,173 +917,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46091.1148611111</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46091.143125</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>125646</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46091.1453125</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="n">
+      <x:c r="F9" s="12" t="n">
         <x:v>123456789</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46091.059537037</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I9" s="15">
         <x:v>46050</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>165163</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46091.0629861111</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="16" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="s"/>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="17" t="s"/>
-      <x:c r="F12" s="17" t="s"/>
+      <x:c r="C12" s="17" t="s"/>
+      <x:c r="D12" s="17" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="18" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="18" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="20" t="s">
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="21" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="24" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,9 +22,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <x:si>
-    <x:t>CERTIFICATE SUMMARY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <x:si>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CERTIFICATES SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>X | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -112,7 +118,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -152,6 +158,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -423,17 +453,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -446,56 +482,56 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -526,75 +562,83 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -823,58 +867,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -917,173 +961,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="F8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46091.1148611111</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>46091.143125</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>125646</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46091.1453125</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="n">
+        <x:v>123456789</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46091.059537037</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46050</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>165163</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46091.0629861111</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="n">
-        <x:v>123456789</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>46091.059537037</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46050</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>165163</x:v>
-      </x:c>
-      <x:c r="K9" s="14" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>46091.0629861111</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s"/>
-      <x:c r="D12" s="17" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="18" t="s"/>
+      <x:c r="B12" s="18" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="20" t="s"/>
-      <x:c r="F13" s="21" t="s">
-        <x:v>25</x:v>
+      <x:c r="B13" s="21" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -2068,7 +2112,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -67,6 +67,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -115,10 +151,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -163,15 +201,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -187,15 +217,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -210,13 +240,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -453,26 +476,26 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -482,56 +505,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -562,83 +588,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -867,78 +901,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -959,7 +1005,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -999,140 +1045,190 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46091.1148611111</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>46091.143125</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>125646</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46091.1453125</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="n">
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="n">
         <x:v>123456789</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
+      <x:c r="G11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>46091.059537037</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I11" s="17">
         <x:v>46050</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>165163</x:v>
       </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L9" s="15">
+      <x:c r="L11" s="19">
         <x:v>46091.0629861111</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="20" t="s"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="20" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
     </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="s">
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
         <x:v>27</x:v>
       </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
-        <x:v>1</x:v>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2109,15 +2205,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="9">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -67,42 +67,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -156,7 +120,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -200,14 +164,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -222,10 +178,18 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -240,6 +204,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -476,7 +447,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -484,16 +455,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -505,13 +476,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -541,10 +506,13 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -557,7 +525,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -588,28 +556,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -624,10 +584,6 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -652,15 +608,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1005,7 +961,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1045,187 +1001,137 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>46091.1148611111</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46091.143125</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>125646</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46091.1453125</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C9" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="E9" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="n">
+        <x:v>123456789</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
+      <x:c r="H9" s="15">
+        <x:v>46091.059537037</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46050</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>165163</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46091.0629861111</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46091.1148611111</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46091.143125</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>125646</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46091.1453125</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="n">
-        <x:v>123456789</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46091.059537037</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46050</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>165163</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46091.0629861111</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="B14" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="s"/>
+      <x:c r="D14" s="18" t="s"/>
+      <x:c r="E14" s="19" t="s"/>
+      <x:c r="F14" s="19" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
-        <x:v>39</x:v>
+      <x:c r="B15" s="20" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="22" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="B16" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="B17" s="23" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="B18" s="26" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -1080,61 +1080,61 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="17" t="s">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="18" t="s"/>
-      <x:c r="D14" s="18" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="19" t="s"/>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="19" t="s"/>
     </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="20" t="s">
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="22" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="n">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="n">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="26" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2116,11 +2116,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -87,6 +87,9 @@
     <x:t>61-3-2026-1403-812</x:t>
   </x:si>
   <x:si>
+    <x:t>125646</x:t>
+  </x:si>
+  <x:si>
     <x:t>cashier edge</x:t>
   </x:si>
   <x:si>
@@ -96,7 +99,13 @@
     <x:t>REN</x:t>
   </x:si>
   <x:si>
+    <x:t>123456789</x:t>
+  </x:si>
+  <x:si>
     <x:t>61-3-2026-1402-290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>165163</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -120,7 +129,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -189,7 +198,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -204,13 +213,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -447,7 +449,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -506,13 +508,10 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -525,7 +524,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -573,6 +572,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -584,6 +587,10 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -608,15 +615,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1009,7 +1016,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
@@ -1021,115 +1028,115 @@
       <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46091.1148611111</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46091.143125</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>125646</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="H8" s="16">
+        <x:v>46091.1148722454</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46091.1431335995</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46091.1453125</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46091.1453198032</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>23</x:v>
+      <x:c r="D9" s="15" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="n">
-        <x:v>123456789</x:v>
+      <x:c r="F9" s="14" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46091.059537037</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46091.0595425347</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46050</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>165163</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46091.0629861111</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46091.0629955324</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="19" t="s"/>
+      <x:c r="B12" s="19" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="s">
-        <x:v>27</x:v>
+      <x:c r="B13" s="22" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="B15" s="25" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="B16" s="28" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -968,7 +968,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1008,7 +1008,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1047,7 +1047,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,15 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
   <x:si>
     <x:t>CERTIFICATES SUMMARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>X | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -449,7 +446,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -466,6 +463,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -524,7 +524,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -560,6 +560,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -934,20 +938,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -970,173 +974,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>46091.1148722454</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46091.1431335995</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46091.1148722454</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46091.1431335995</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46091.1453198032</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46091.1453198032</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
+      <x:c r="E9" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>46091.0595425347</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46050</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46091.0595425347</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46050</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="18" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>46091.0629955324</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="21" t="s"/>
+      <x:c r="B12" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="22" t="s">
+      <x:c r="B13" s="23" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
+      <x:c r="B15" s="26" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="29" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -126,7 +126,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -166,14 +166,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -446,7 +438,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -457,16 +449,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -478,53 +467,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -559,87 +548,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -941,17 +926,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -974,173 +959,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46091.1148722454</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46091.1431335995</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46091.1453198032</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46091.0595425347</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46050</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46091.0629955324</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-certificateRows_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -66,18 +66,36 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
+    <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDISSA ABASTAS AMANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brgy 4, City Of Koronadal (Capital), South Cotabato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123456789</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1402-290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>165163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cashier edge</x:t>
+  </x:si>
+  <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
   </x:si>
   <x:si>
-    <x:t>EDISSA ABASTAS AMANTE</x:t>
-  </x:si>
-  <x:si>
     <x:t>NEW</x:t>
   </x:si>
   <x:si>
-    <x:t>Brgy 4, City Of Koronadal (Capital), South Cotabato</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-X-06965</x:t>
   </x:si>
   <x:si>
@@ -85,24 +103,6 @@
   </x:si>
   <x:si>
     <x:t>125646</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cashier edge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123456789</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-3-2026-1402-290</x:t>
-  </x:si>
-  <x:si>
-    <x:t>165163</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -1018,19 +1018,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46091.1148722454</x:v>
+        <x:v>46091.0595425347</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46091.1431335995</x:v>
+        <x:v>46050</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>210</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46091.1453198032</x:v>
+        <x:v>46091.0629955324</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
@@ -1056,19 +1056,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46091.0595425347</x:v>
+        <x:v>46091.1148722454</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46050</x:v>
+        <x:v>46091.1431335995</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>300</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46091.0629955324</x:v>
+        <x:v>46091.1453198032</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
@@ -1098,7 +1098,7 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
       <x:c r="B14" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="26" t="s"/>
       <x:c r="D14" s="26" t="s"/>
@@ -1109,7 +1109,7 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
       <x:c r="B15" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="26" t="s"/>
       <x:c r="D15" s="26" t="s"/>
